--- a/ЛР2-3_Объем_рынка/Excel/ПК_потенциальные_клиенты_NotaCode.xlsx
+++ b/ЛР2-3_Объем_рынка/Excel/ПК_потенциальные_клиенты_NotaCode.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ИИТ\ЭлектронныйБизнес\ЛР2-3_Объем_рынка\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ИИТ\ЭлектронныйБизнес\ЛР2-3_Объем_рынка\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75B6D0A6-B936-4F7C-884F-ED4A887F77F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64DCAD56-7C9E-4E15-B217-B5AF06FF4BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="3975" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_Методика" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,20 @@
     <sheet name="08_Справочник" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029" refMode="R1C1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1877,7 +1891,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z200"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="84.25" customWidth="1"/>
     <col min="2" max="2" width="62" customWidth="1"/>
@@ -1885,7 +1899,7 @@
     <col min="4" max="4" width="39.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="18">
+    <row r="1" spans="1:26" ht="17.649999999999999">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1943,7 +1957,7 @@
       <c r="Y2" s="9"/>
       <c r="Z2" s="9"/>
     </row>
-    <row r="3" spans="1:26" ht="15">
+    <row r="3" spans="1:26" ht="13.9">
       <c r="A3" s="18" t="s">
         <v>1</v>
       </c>
@@ -1973,7 +1987,7 @@
       <c r="Y3" s="9"/>
       <c r="Z3" s="9"/>
     </row>
-    <row r="4" spans="1:26" ht="42.75">
+    <row r="4" spans="1:26" ht="40.5">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -2005,7 +2019,7 @@
       <c r="Y4" s="9"/>
       <c r="Z4" s="9"/>
     </row>
-    <row r="5" spans="1:26" ht="57">
+    <row r="5" spans="1:26" ht="54">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -2037,7 +2051,7 @@
       <c r="Y5" s="9"/>
       <c r="Z5" s="9"/>
     </row>
-    <row r="6" spans="1:26" ht="42.75">
+    <row r="6" spans="1:26" ht="40.5">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
@@ -2069,7 +2083,7 @@
       <c r="Y6" s="9"/>
       <c r="Z6" s="9"/>
     </row>
-    <row r="7" spans="1:26" ht="28.5">
+    <row r="7" spans="1:26" ht="27">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -2101,7 +2115,7 @@
       <c r="Y7" s="9"/>
       <c r="Z7" s="9"/>
     </row>
-    <row r="8" spans="1:26" ht="57">
+    <row r="8" spans="1:26" ht="54">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -2161,7 +2175,7 @@
       <c r="Y9" s="9"/>
       <c r="Z9" s="9"/>
     </row>
-    <row r="10" spans="1:26" ht="15">
+    <row r="10" spans="1:26" ht="13.9">
       <c r="A10" s="18" t="s">
         <v>12</v>
       </c>
@@ -2191,7 +2205,7 @@
       <c r="Y10" s="9"/>
       <c r="Z10" s="9"/>
     </row>
-    <row r="11" spans="1:26" ht="15">
+    <row r="11" spans="1:26" ht="13.9">
       <c r="A11" s="2" t="s">
         <v>13</v>
       </c>
@@ -2227,7 +2241,7 @@
       <c r="Y11" s="9"/>
       <c r="Z11" s="9"/>
     </row>
-    <row r="12" spans="1:26" ht="28.5">
+    <row r="12" spans="1:26" ht="27">
       <c r="A12" s="10">
         <v>1</v>
       </c>
@@ -2299,7 +2313,7 @@
       <c r="Y13" s="9"/>
       <c r="Z13" s="9"/>
     </row>
-    <row r="14" spans="1:26" ht="28.5">
+    <row r="14" spans="1:26" ht="27">
       <c r="A14" s="10">
         <v>3</v>
       </c>
@@ -2335,7 +2349,7 @@
       <c r="Y14" s="9"/>
       <c r="Z14" s="9"/>
     </row>
-    <row r="15" spans="1:26" ht="28.5">
+    <row r="15" spans="1:26" ht="27">
       <c r="A15" s="10">
         <v>4</v>
       </c>
@@ -2407,7 +2421,7 @@
       <c r="Y16" s="9"/>
       <c r="Z16" s="9"/>
     </row>
-    <row r="17" spans="1:26" ht="28.5">
+    <row r="17" spans="1:26">
       <c r="A17" s="10">
         <v>6</v>
       </c>
@@ -2499,7 +2513,7 @@
       <c r="Y19" s="9"/>
       <c r="Z19" s="9"/>
     </row>
-    <row r="20" spans="1:26" ht="15">
+    <row r="20" spans="1:26" ht="13.9">
       <c r="A20" s="18" t="s">
         <v>35</v>
       </c>
@@ -2529,7 +2543,7 @@
       <c r="Y20" s="9"/>
       <c r="Z20" s="9"/>
     </row>
-    <row r="21" spans="1:26" ht="15">
+    <row r="21" spans="1:26" ht="13.9">
       <c r="A21" s="2" t="s">
         <v>36</v>
       </c>
@@ -2561,7 +2575,7 @@
       <c r="Y21" s="9"/>
       <c r="Z21" s="9"/>
     </row>
-    <row r="22" spans="1:26" ht="28.5">
+    <row r="22" spans="1:26" ht="27">
       <c r="A22" s="10" t="s">
         <v>38</v>
       </c>
@@ -2593,7 +2607,7 @@
       <c r="Y22" s="9"/>
       <c r="Z22" s="9"/>
     </row>
-    <row r="23" spans="1:26" ht="28.5">
+    <row r="23" spans="1:26" ht="27">
       <c r="A23" s="10" t="s">
         <v>40</v>
       </c>
@@ -2625,7 +2639,7 @@
       <c r="Y23" s="9"/>
       <c r="Z23" s="9"/>
     </row>
-    <row r="24" spans="1:26" ht="28.5">
+    <row r="24" spans="1:26" ht="27">
       <c r="A24" s="10" t="s">
         <v>42</v>
       </c>
@@ -2657,7 +2671,7 @@
       <c r="Y24" s="9"/>
       <c r="Z24" s="9"/>
     </row>
-    <row r="25" spans="1:26" ht="28.5">
+    <row r="25" spans="1:26" ht="27">
       <c r="A25" s="10" t="s">
         <v>44</v>
       </c>
@@ -2689,7 +2703,7 @@
       <c r="Y25" s="9"/>
       <c r="Z25" s="9"/>
     </row>
-    <row r="26" spans="1:26" ht="28.5">
+    <row r="26" spans="1:26" ht="27">
       <c r="A26" s="10" t="s">
         <v>46</v>
       </c>
@@ -7607,14 +7621,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z200"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
     <col min="3" max="4" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="18">
+    <row r="1" spans="1:26" ht="17.649999999999999">
       <c r="A1" s="17" t="s">
         <v>48</v>
       </c>
@@ -7672,7 +7686,7 @@
       <c r="Y2" s="9"/>
       <c r="Z2" s="9"/>
     </row>
-    <row r="3" spans="1:26" ht="15">
+    <row r="3" spans="1:26" ht="13.9">
       <c r="A3" s="2" t="s">
         <v>49</v>
       </c>
@@ -7708,7 +7722,7 @@
       <c r="Y3" s="9"/>
       <c r="Z3" s="9"/>
     </row>
-    <row r="4" spans="1:26" ht="42.75">
+    <row r="4" spans="1:26" ht="40.5">
       <c r="A4" s="11" t="s">
         <v>53</v>
       </c>
@@ -7744,7 +7758,7 @@
       <c r="Y4" s="9"/>
       <c r="Z4" s="9"/>
     </row>
-    <row r="5" spans="1:26" ht="28.5">
+    <row r="5" spans="1:26" ht="27">
       <c r="A5" s="11" t="s">
         <v>56</v>
       </c>
@@ -7780,7 +7794,7 @@
       <c r="Y5" s="9"/>
       <c r="Z5" s="9"/>
     </row>
-    <row r="6" spans="1:26" ht="99.75">
+    <row r="6" spans="1:26" ht="94.5">
       <c r="A6" s="11" t="s">
         <v>59</v>
       </c>
@@ -7816,7 +7830,7 @@
       <c r="Y6" s="9"/>
       <c r="Z6" s="9"/>
     </row>
-    <row r="7" spans="1:26" ht="28.5">
+    <row r="7" spans="1:26" ht="27">
       <c r="A7" s="11" t="s">
         <v>62</v>
       </c>
@@ -7852,7 +7866,7 @@
       <c r="Y7" s="9"/>
       <c r="Z7" s="9"/>
     </row>
-    <row r="8" spans="1:26" ht="28.5">
+    <row r="8" spans="1:26" ht="27">
       <c r="A8" s="11" t="s">
         <v>65</v>
       </c>
@@ -7888,7 +7902,7 @@
       <c r="Y8" s="9"/>
       <c r="Z8" s="9"/>
     </row>
-    <row r="9" spans="1:26" ht="15">
+    <row r="9" spans="1:26" ht="13.9">
       <c r="A9" s="11" t="s">
         <v>68</v>
       </c>
@@ -7924,7 +7938,7 @@
       <c r="Y9" s="9"/>
       <c r="Z9" s="9"/>
     </row>
-    <row r="10" spans="1:26" ht="28.5">
+    <row r="10" spans="1:26" ht="27">
       <c r="A10" s="11" t="s">
         <v>72</v>
       </c>
@@ -7960,12 +7974,12 @@
       <c r="Y10" s="9"/>
       <c r="Z10" s="9"/>
     </row>
-    <row r="11" spans="1:26" ht="15">
+    <row r="11" spans="1:26" ht="13.9">
       <c r="A11" s="11" t="s">
         <v>75</v>
       </c>
       <c r="B11" s="4">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>76</v>
@@ -7996,7 +8010,7 @@
       <c r="Y11" s="9"/>
       <c r="Z11" s="9"/>
     </row>
-    <row r="12" spans="1:26" ht="15">
+    <row r="12" spans="1:26" ht="13.9">
       <c r="A12" s="11" t="s">
         <v>78</v>
       </c>
@@ -8086,7 +8100,7 @@
       <c r="Y14" s="9"/>
       <c r="Z14" s="9"/>
     </row>
-    <row r="15" spans="1:26" ht="15">
+    <row r="15" spans="1:26" ht="13.9">
       <c r="A15" s="18" t="s">
         <v>80</v>
       </c>
@@ -8116,7 +8130,7 @@
       <c r="Y15" s="9"/>
       <c r="Z15" s="9"/>
     </row>
-    <row r="16" spans="1:26" ht="15">
+    <row r="16" spans="1:26" ht="13.9">
       <c r="A16" s="2" t="s">
         <v>81</v>
       </c>
@@ -8148,7 +8162,7 @@
       <c r="Y16" s="9"/>
       <c r="Z16" s="9"/>
     </row>
-    <row r="17" spans="1:26" ht="28.5">
+    <row r="17" spans="1:26" ht="27">
       <c r="A17" s="10" t="s">
         <v>82</v>
       </c>
@@ -8180,7 +8194,7 @@
       <c r="Y17" s="9"/>
       <c r="Z17" s="9"/>
     </row>
-    <row r="18" spans="1:26" ht="42.75">
+    <row r="18" spans="1:26" ht="27">
       <c r="A18" s="10" t="s">
         <v>84</v>
       </c>
@@ -8276,7 +8290,7 @@
       <c r="Y20" s="9"/>
       <c r="Z20" s="9"/>
     </row>
-    <row r="21" spans="1:26" ht="28.5">
+    <row r="21" spans="1:26">
       <c r="A21" s="10" t="s">
         <v>40</v>
       </c>
@@ -8308,7 +8322,7 @@
       <c r="Y21" s="9"/>
       <c r="Z21" s="9"/>
     </row>
-    <row r="22" spans="1:26" ht="28.5">
+    <row r="22" spans="1:26" ht="27">
       <c r="A22" s="10" t="s">
         <v>42</v>
       </c>
@@ -13336,7 +13350,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Z200"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -13351,7 +13365,7 @@
     <col min="17" max="17" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="18">
+    <row r="1" spans="1:26" ht="17.649999999999999">
       <c r="A1" s="17" t="s">
         <v>92</v>
       </c>
@@ -13409,7 +13423,7 @@
       <c r="Y2" s="9"/>
       <c r="Z2" s="9"/>
     </row>
-    <row r="3" spans="1:26" ht="45">
+    <row r="3" spans="1:26" ht="41.65">
       <c r="A3" s="2" t="s">
         <v>93</v>
       </c>
@@ -13471,7 +13485,7 @@
       <c r="Y3" s="9"/>
       <c r="Z3" s="9"/>
     </row>
-    <row r="4" spans="1:26" ht="57">
+    <row r="4" spans="1:26" ht="54">
       <c r="A4" s="10" t="s">
         <v>221</v>
       </c>
@@ -13537,7 +13551,7 @@
       <c r="Y4" s="9"/>
       <c r="Z4" s="9"/>
     </row>
-    <row r="5" spans="1:26" ht="57">
+    <row r="5" spans="1:26" ht="54">
       <c r="A5" s="10" t="s">
         <v>223</v>
       </c>
@@ -13603,7 +13617,7 @@
       <c r="Y5" s="9"/>
       <c r="Z5" s="9"/>
     </row>
-    <row r="6" spans="1:26" ht="57">
+    <row r="6" spans="1:26" ht="54">
       <c r="A6" s="10" t="s">
         <v>225</v>
       </c>
@@ -13857,7 +13871,7 @@
       <c r="Y11" s="9"/>
       <c r="Z11" s="9"/>
     </row>
-    <row r="12" spans="1:26" ht="15">
+    <row r="12" spans="1:26" ht="13.9">
       <c r="A12" s="1" t="s">
         <v>112</v>
       </c>
@@ -19270,14 +19284,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Z200"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="10" width="14" customWidth="1"/>
     <col min="11" max="11" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="18">
+    <row r="1" spans="1:26" ht="17.649999999999999">
       <c r="A1" s="17" t="s">
         <v>113</v>
       </c>
@@ -19335,7 +19349,7 @@
       <c r="Y2" s="9"/>
       <c r="Z2" s="9"/>
     </row>
-    <row r="3" spans="1:26" ht="45">
+    <row r="3" spans="1:26" ht="41.65">
       <c r="A3" s="2" t="s">
         <v>114</v>
       </c>
@@ -19385,7 +19399,7 @@
       <c r="Y3" s="9"/>
       <c r="Z3" s="9"/>
     </row>
-    <row r="4" spans="1:26" ht="42.75">
+    <row r="4" spans="1:26" ht="40.5">
       <c r="A4" s="10" t="s">
         <v>121</v>
       </c>
@@ -19438,7 +19452,7 @@
       <c r="Y4" s="9"/>
       <c r="Z4" s="9"/>
     </row>
-    <row r="5" spans="1:26" ht="28.5">
+    <row r="5" spans="1:26" ht="27">
       <c r="A5" s="10" t="s">
         <v>123</v>
       </c>
@@ -19491,7 +19505,7 @@
       <c r="Y5" s="9"/>
       <c r="Z5" s="9"/>
     </row>
-    <row r="6" spans="1:26" ht="42.75">
+    <row r="6" spans="1:26" ht="40.5">
       <c r="A6" s="10" t="s">
         <v>125</v>
       </c>
@@ -25028,7 +25042,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:Z200"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="46" customWidth="1"/>
@@ -25036,7 +25050,7 @@
     <col min="4" max="4" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="18">
+    <row r="1" spans="1:26" ht="17.649999999999999">
       <c r="A1" s="17" t="s">
         <v>127</v>
       </c>
@@ -25094,7 +25108,7 @@
       <c r="Y2" s="9"/>
       <c r="Z2" s="9"/>
     </row>
-    <row r="3" spans="1:26" ht="15">
+    <row r="3" spans="1:26" ht="13.9">
       <c r="A3" s="2" t="s">
         <v>36</v>
       </c>
@@ -25130,7 +25144,7 @@
       <c r="Y3" s="9"/>
       <c r="Z3" s="9"/>
     </row>
-    <row r="4" spans="1:26" ht="28.5">
+    <row r="4" spans="1:26" ht="27">
       <c r="A4" s="10" t="s">
         <v>130</v>
       </c>
@@ -25167,7 +25181,7 @@
       <c r="Y4" s="9"/>
       <c r="Z4" s="9"/>
     </row>
-    <row r="5" spans="1:26" ht="28.5">
+    <row r="5" spans="1:26" ht="27">
       <c r="A5" s="10" t="s">
         <v>133</v>
       </c>
@@ -25204,7 +25218,7 @@
       <c r="Y5" s="9"/>
       <c r="Z5" s="9"/>
     </row>
-    <row r="6" spans="1:26" ht="28.5">
+    <row r="6" spans="1:26" ht="27">
       <c r="A6" s="10" t="s">
         <v>136</v>
       </c>
@@ -25241,7 +25255,7 @@
       <c r="Y6" s="9"/>
       <c r="Z6" s="9"/>
     </row>
-    <row r="7" spans="1:26" ht="28.5">
+    <row r="7" spans="1:26" ht="27">
       <c r="A7" s="10" t="s">
         <v>40</v>
       </c>
@@ -25408,7 +25422,7 @@
       <c r="Y11" s="9"/>
       <c r="Z11" s="9"/>
     </row>
-    <row r="12" spans="1:26" ht="15">
+    <row r="12" spans="1:26" ht="13.9">
       <c r="A12" s="18" t="s">
         <v>146</v>
       </c>
@@ -25438,7 +25452,7 @@
       <c r="Y12" s="9"/>
       <c r="Z12" s="9"/>
     </row>
-    <row r="13" spans="1:26" ht="15">
+    <row r="13" spans="1:26" ht="13.9">
       <c r="A13" s="2" t="s">
         <v>147</v>
       </c>
@@ -25474,7 +25488,7 @@
       <c r="Y13" s="9"/>
       <c r="Z13" s="9"/>
     </row>
-    <row r="14" spans="1:26" ht="28.5">
+    <row r="14" spans="1:26" ht="27">
       <c r="A14" s="10" t="s">
         <v>150</v>
       </c>
@@ -25511,7 +25525,7 @@
       <c r="Y14" s="9"/>
       <c r="Z14" s="9"/>
     </row>
-    <row r="15" spans="1:26" ht="28.5">
+    <row r="15" spans="1:26" ht="27">
       <c r="A15" s="10" t="s">
         <v>153</v>
       </c>
@@ -25548,7 +25562,7 @@
       <c r="Y15" s="9"/>
       <c r="Z15" s="9"/>
     </row>
-    <row r="16" spans="1:26" ht="28.5">
+    <row r="16" spans="1:26" ht="27">
       <c r="A16" s="10" t="s">
         <v>156</v>
       </c>
@@ -30749,7 +30763,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:Z200"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -30763,7 +30777,7 @@
     <col min="12" max="15" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="18">
+    <row r="1" spans="1:26" ht="17.649999999999999">
       <c r="A1" s="17" t="s">
         <v>159</v>
       </c>
@@ -30821,7 +30835,7 @@
       <c r="Y2" s="9"/>
       <c r="Z2" s="9"/>
     </row>
-    <row r="3" spans="1:26" ht="60">
+    <row r="3" spans="1:26" ht="41.65">
       <c r="A3" s="2" t="s">
         <v>160</v>
       </c>
@@ -30879,7 +30893,7 @@
       <c r="Y3" s="9"/>
       <c r="Z3" s="9"/>
     </row>
-    <row r="4" spans="1:26" ht="28.5">
+    <row r="4" spans="1:26" ht="27">
       <c r="A4" s="10" t="s">
         <v>229</v>
       </c>
@@ -30942,7 +30956,7 @@
       <c r="Y4" s="9"/>
       <c r="Z4" s="9"/>
     </row>
-    <row r="5" spans="1:26" ht="28.5">
+    <row r="5" spans="1:26" ht="27">
       <c r="A5" s="10" t="s">
         <v>232</v>
       </c>
@@ -31005,7 +31019,7 @@
       <c r="Y5" s="9"/>
       <c r="Z5" s="9"/>
     </row>
-    <row r="6" spans="1:26" ht="28.5">
+    <row r="6" spans="1:26" ht="27">
       <c r="A6" s="10" t="s">
         <v>235</v>
       </c>
@@ -31068,7 +31082,7 @@
       <c r="Y6" s="9"/>
       <c r="Z6" s="9"/>
     </row>
-    <row r="7" spans="1:26" ht="28.5">
+    <row r="7" spans="1:26" ht="27">
       <c r="A7" s="10" t="s">
         <v>238</v>
       </c>
@@ -31202,7 +31216,7 @@
       <c r="Y9" s="9"/>
       <c r="Z9" s="9"/>
     </row>
-    <row r="10" spans="1:26" ht="15">
+    <row r="10" spans="1:26" ht="13.9">
       <c r="A10" s="1" t="s">
         <v>174</v>
       </c>
@@ -31278,7 +31292,7 @@
       <c r="Y11" s="9"/>
       <c r="Z11" s="9"/>
     </row>
-    <row r="12" spans="1:26" ht="45">
+    <row r="12" spans="1:26" ht="41.65">
       <c r="A12" s="1" t="s">
         <v>175</v>
       </c>
@@ -36661,7 +36675,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:Z200"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -36673,7 +36687,7 @@
     <col min="9" max="9" width="6.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="18">
+    <row r="1" spans="1:26" ht="17.649999999999999">
       <c r="A1" s="17" t="s">
         <v>176</v>
       </c>
@@ -36731,7 +36745,7 @@
       <c r="Y2" s="9"/>
       <c r="Z2" s="9"/>
     </row>
-    <row r="3" spans="1:26" ht="15">
+    <row r="3" spans="1:26" ht="13.9">
       <c r="A3" s="2" t="s">
         <v>36</v>
       </c>
@@ -36767,7 +36781,7 @@
       <c r="Y3" s="9"/>
       <c r="Z3" s="9"/>
     </row>
-    <row r="4" spans="1:26" ht="15">
+    <row r="4" spans="1:26" ht="13.9">
       <c r="A4" s="10" t="s">
         <v>38</v>
       </c>
@@ -36808,7 +36822,7 @@
       <c r="Y4" s="9"/>
       <c r="Z4" s="9"/>
     </row>
-    <row r="5" spans="1:26" ht="28.5">
+    <row r="5" spans="1:26" ht="27">
       <c r="A5" s="10" t="s">
         <v>40</v>
       </c>
@@ -36852,7 +36866,7 @@
       <c r="Y5" s="9"/>
       <c r="Z5" s="9"/>
     </row>
-    <row r="6" spans="1:26" ht="28.5">
+    <row r="6" spans="1:26" ht="27">
       <c r="A6" s="10" t="s">
         <v>42</v>
       </c>
@@ -36896,7 +36910,7 @@
       <c r="Y6" s="9"/>
       <c r="Z6" s="9"/>
     </row>
-    <row r="7" spans="1:26" ht="28.5">
+    <row r="7" spans="1:26" ht="27">
       <c r="A7" s="10" t="s">
         <v>182</v>
       </c>
@@ -36940,7 +36954,7 @@
       <c r="Y7" s="9"/>
       <c r="Z7" s="9"/>
     </row>
-    <row r="8" spans="1:26" ht="28.5">
+    <row r="8" spans="1:26" ht="27">
       <c r="A8" s="10" t="s">
         <v>184</v>
       </c>
@@ -37093,7 +37107,7 @@
       <c r="Y11" s="9"/>
       <c r="Z11" s="9"/>
     </row>
-    <row r="12" spans="1:26" ht="15">
+    <row r="12" spans="1:26" ht="13.9">
       <c r="A12" s="18" t="s">
         <v>187</v>
       </c>
@@ -37123,7 +37137,7 @@
       <c r="Y12" s="9"/>
       <c r="Z12" s="9"/>
     </row>
-    <row r="13" spans="1:26" ht="15">
+    <row r="13" spans="1:26" ht="13.9">
       <c r="A13" s="2" t="s">
         <v>114</v>
       </c>
@@ -37161,7 +37175,7 @@
       <c r="Y13" s="9"/>
       <c r="Z13" s="9"/>
     </row>
-    <row r="14" spans="1:26" ht="28.5">
+    <row r="14" spans="1:26" ht="27">
       <c r="A14" s="10" t="s">
         <v>121</v>
       </c>
@@ -37340,7 +37354,7 @@
       <c r="Y18" s="9"/>
       <c r="Z18" s="9"/>
     </row>
-    <row r="19" spans="1:26" ht="15">
+    <row r="19" spans="1:26" ht="13.9">
       <c r="A19" s="18" t="s">
         <v>192</v>
       </c>
@@ -42456,7 +42470,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:Z200"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -42468,7 +42482,7 @@
     <col min="8" max="8" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="18">
+    <row r="1" spans="1:26" ht="17.649999999999999">
       <c r="A1" s="17" t="s">
         <v>193</v>
       </c>
@@ -42526,7 +42540,7 @@
       <c r="Y2" s="9"/>
       <c r="Z2" s="9"/>
     </row>
-    <row r="3" spans="1:26" ht="30">
+    <row r="3" spans="1:26" ht="27.75">
       <c r="A3" s="2" t="s">
         <v>194</v>
       </c>
@@ -42570,7 +42584,7 @@
       <c r="Y3" s="9"/>
       <c r="Z3" s="9"/>
     </row>
-    <row r="4" spans="1:26" ht="28.5">
+    <row r="4" spans="1:26" ht="27">
       <c r="A4" s="10" t="s">
         <v>82</v>
       </c>
@@ -42584,7 +42598,7 @@
         <v>242</v>
       </c>
       <c r="E4" s="16">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>243</v>
@@ -42614,7 +42628,7 @@
       <c r="Y4" s="9"/>
       <c r="Z4" s="9"/>
     </row>
-    <row r="5" spans="1:26" ht="57">
+    <row r="5" spans="1:26" ht="54">
       <c r="A5" s="10" t="s">
         <v>82</v>
       </c>
@@ -42628,7 +42642,7 @@
         <v>246</v>
       </c>
       <c r="E5" s="16">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>243</v>
@@ -42658,7 +42672,7 @@
       <c r="Y5" s="9"/>
       <c r="Z5" s="9"/>
     </row>
-    <row r="6" spans="1:26" ht="28.5">
+    <row r="6" spans="1:26" ht="27">
       <c r="A6" s="10" t="s">
         <v>82</v>
       </c>
@@ -42672,7 +42686,7 @@
         <v>249</v>
       </c>
       <c r="E6" s="16">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>243</v>
@@ -42702,7 +42716,7 @@
       <c r="Y6" s="9"/>
       <c r="Z6" s="9"/>
     </row>
-    <row r="7" spans="1:26" ht="42.75">
+    <row r="7" spans="1:26" ht="40.5">
       <c r="A7" s="10" t="s">
         <v>250</v>
       </c>
@@ -42716,7 +42730,7 @@
         <v>253</v>
       </c>
       <c r="E7" s="16">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>254</v>
@@ -42746,7 +42760,7 @@
       <c r="Y7" s="9"/>
       <c r="Z7" s="9"/>
     </row>
-    <row r="8" spans="1:26" ht="28.5">
+    <row r="8" spans="1:26" ht="27">
       <c r="A8" s="10" t="s">
         <v>255</v>
       </c>
@@ -42760,7 +42774,7 @@
         <v>258</v>
       </c>
       <c r="E8" s="16">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>254</v>
@@ -42790,7 +42804,7 @@
       <c r="Y8" s="9"/>
       <c r="Z8" s="9"/>
     </row>
-    <row r="9" spans="1:26" ht="42.75">
+    <row r="9" spans="1:26" ht="40.5">
       <c r="A9" s="10" t="s">
         <v>259</v>
       </c>
@@ -42804,7 +42818,7 @@
         <v>261</v>
       </c>
       <c r="E9" s="16">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>254</v>
@@ -42834,7 +42848,7 @@
       <c r="Y9" s="9"/>
       <c r="Z9" s="9"/>
     </row>
-    <row r="10" spans="1:26" ht="42.75">
+    <row r="10" spans="1:26" ht="40.5">
       <c r="A10" s="10" t="s">
         <v>262</v>
       </c>
@@ -42848,7 +42862,7 @@
         <v>265</v>
       </c>
       <c r="E10" s="16">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>254</v>
@@ -42876,7 +42890,7 @@
       <c r="Y10" s="9"/>
       <c r="Z10" s="9"/>
     </row>
-    <row r="11" spans="1:26" ht="57">
+    <row r="11" spans="1:26" ht="54">
       <c r="A11" s="10" t="s">
         <v>86</v>
       </c>
@@ -42890,7 +42904,7 @@
         <v>266</v>
       </c>
       <c r="E11" s="16">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>267</v>
@@ -42918,7 +42932,7 @@
       <c r="Y11" s="9"/>
       <c r="Z11" s="9"/>
     </row>
-    <row r="12" spans="1:26" ht="28.5">
+    <row r="12" spans="1:26" ht="27">
       <c r="A12" s="10" t="s">
         <v>207</v>
       </c>
@@ -42932,7 +42946,7 @@
         <v>270</v>
       </c>
       <c r="E12" s="16">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>271</v>
@@ -42960,7 +42974,7 @@
       <c r="Y12" s="9"/>
       <c r="Z12" s="9"/>
     </row>
-    <row r="13" spans="1:26" ht="42.75">
+    <row r="13" spans="1:26" ht="40.5">
       <c r="A13" s="10" t="s">
         <v>272</v>
       </c>
@@ -42974,7 +42988,7 @@
         <v>273</v>
       </c>
       <c r="E13" s="16">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>254</v>
@@ -48270,7 +48284,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:Z200"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="48.625" customWidth="1"/>
     <col min="2" max="2" width="19.625" customWidth="1"/>
@@ -48278,7 +48292,7 @@
     <col min="4" max="4" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="18">
+    <row r="1" spans="1:26" ht="17.649999999999999">
       <c r="A1" s="17" t="s">
         <v>209</v>
       </c>
@@ -48336,7 +48350,7 @@
       <c r="Y2" s="9"/>
       <c r="Z2" s="9"/>
     </row>
-    <row r="3" spans="1:26" ht="30">
+    <row r="3" spans="1:26" ht="27.75">
       <c r="A3" s="2" t="s">
         <v>94</v>
       </c>
